--- a/docs/05_etc/予定進捗.xlsx
+++ b/docs/05_etc/予定進捗.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8D2F314-03A5-429A-A0B1-CC78DA84C488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AA7B1F0-7D4B-4CF8-BBE8-140F68BBAACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A8452A5F-21C4-4EF5-A594-E961C9578935}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{A8452A5F-21C4-4EF5-A594-E961C9578935}"/>
   </bookViews>
   <sheets>
     <sheet name="予定" sheetId="2" r:id="rId1"/>
@@ -156,7 +156,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -178,6 +178,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -203,9 +209,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -213,6 +216,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -233,9 +239,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -273,7 +279,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -379,7 +385,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -521,7 +527,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -646,37 +652,21 @@
       <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
+      <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
@@ -685,33 +675,21 @@
       <c r="B6" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" t="s">
         <v>8</v>
       </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="2"/>
+      <c r="H8" s="2"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
@@ -720,21 +698,21 @@
       <c r="B9" t="s">
         <v>6</v>
       </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" t="s">
         <v>7</v>
       </c>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" t="s">
         <v>8</v>
       </c>
-      <c r="J11" s="3"/>
+      <c r="J11" s="2"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
@@ -743,118 +721,110 @@
       <c r="B12" t="s">
         <v>6</v>
       </c>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" t="s">
         <v>7</v>
       </c>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="L14" s="3"/>
-      <c r="N14" s="2"/>
+      <c r="L14" s="2"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="4"/>
-      <c r="Q15" s="4"/>
-      <c r="R15" s="4"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="3"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4" t="s">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
-      <c r="N16" s="4"/>
-      <c r="O16" s="4"/>
-      <c r="P16" s="4"/>
-      <c r="Q16" s="4"/>
-      <c r="R16" s="4"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4" t="s">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
-      <c r="O17" s="4"/>
-      <c r="P17" s="4"/>
-      <c r="Q17" s="4"/>
-      <c r="R17" s="4"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" t="s">
         <v>13</v>
       </c>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" t="s">
         <v>14</v>
       </c>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="B20" t="s">
         <v>0</v>
       </c>
-      <c r="Q20" s="3"/>
-      <c r="R20" s="3"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -981,46 +951,22 @@
       <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
+      <c r="F5" s="5"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
@@ -1029,46 +975,16 @@
       <c r="B6" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
@@ -1077,46 +993,16 @@
       <c r="B9" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
@@ -1125,144 +1011,99 @@
       <c r="B12" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="4"/>
-      <c r="Q15" s="4"/>
-      <c r="R15" s="4"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="3"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4" t="s">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
-      <c r="N16" s="4"/>
-      <c r="O16" s="4"/>
-      <c r="P16" s="4"/>
-      <c r="Q16" s="4"/>
-      <c r="R16" s="4"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4" t="s">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
-      <c r="O17" s="4"/>
-      <c r="P17" s="4"/>
-      <c r="Q17" s="4"/>
-      <c r="R17" s="4"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" t="s">
         <v>13</v>
       </c>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
-      <c r="P18" s="2"/>
-      <c r="Q18" s="2"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" t="s">
         <v>14</v>
       </c>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-      <c r="P19" s="2"/>
-      <c r="Q19" s="2"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="B20" t="s">
         <v>0</v>
       </c>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
-      <c r="P20" s="2"/>
-      <c r="Q20" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
